--- a/ML2025Spring/最終分數.xlsx
+++ b/ML2025Spring/最終分數.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t xml:space="preserve">Private Score</t>
   </si>
@@ -105,11 +105,26 @@
 PDR ≥ 0.85</t>
   </si>
   <si>
+    <t xml:space="preserve">Strong
+FID ≤ 73.00
+PDR ≥ 0.85</t>
+  </si>
+  <si>
     <t xml:space="preserve">使用大模型，再搭配 data augmentation
 個人依生成的圖感覺應該有 Strong</t>
   </si>
   <si>
     <t xml:space="preserve">HW05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4o-mini score
+Simple 2.4
+Medium 4.15
+Strong 4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong
+Gemini 評估：平均分數為：4.99/10</t>
   </si>
   <si>
     <t xml:space="preserve">num_train_epochs &amp; learning_rate 不要太大
@@ -119,6 +134,38 @@
   </si>
   <si>
     <t xml:space="preserve">HW06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong 0.455
+Safety Rate 0.725</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Strong
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GSM Public 0.538
+Gemini 評估：安全/改善/不安全 
+197/39/4: 197/240=0.8208</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">重點在 MajorityVoting，可讓數學正確率提升
+又不至於訓練過度導致 Safety 下降</t>
   </si>
   <si>
     <t xml:space="preserve">HW07</t>
@@ -155,7 +202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -167,19 +214,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
@@ -193,6 +237,25 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -238,7 +301,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -265,6 +328,14 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -391,11 +462,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1000"/>
-  <sheetFormatPr defaultColWidth="12.10546875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="57.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="36.73"/>
@@ -426,7 +498,7 @@
       </c>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -447,7 +519,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -496,45 +568,55 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="68.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -547,7 +629,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -560,7 +642,7 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -573,7 +655,7 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -586,7 +668,7 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -599,7 +681,7 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -612,7 +694,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -625,7 +707,7 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -638,7 +720,7 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>

--- a/ML2025Spring/最終分數.xlsx
+++ b/ML2025Spring/最終分數.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t xml:space="preserve">Private Score</t>
   </si>
@@ -97,6 +97,9 @@
     <t xml:space="preserve">HW03</t>
   </si>
   <si>
+    <t xml:space="preserve">Q &amp; A</t>
+  </si>
+  <si>
     <t xml:space="preserve">HW04</t>
   </si>
   <si>
@@ -140,28 +143,10 @@
 Safety Rate 0.725</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Strong
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GSM Public 0.538
+    <t xml:space="preserve">Strong
+GSM Public 0.538
 Gemini 評估：安全/改善/不安全 
 197/39/4: 197/240=0.8208</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">重點在 MajorityVoting，可讓數學正確率提升
@@ -202,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -214,16 +199,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
@@ -240,18 +228,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
@@ -259,12 +235,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -330,11 +312,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -462,11 +444,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1000"/>
-  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.11328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="57.63"/>
@@ -498,7 +480,7 @@
       </c>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="17.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -519,7 +501,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -548,88 +530,92 @@
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="53.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>21</v>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="68.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -642,7 +628,7 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -655,7 +641,7 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -668,7 +654,7 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -681,7 +667,7 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -694,7 +680,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -707,7 +693,7 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -720,7 +706,7 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>

--- a/ML2025Spring/最終分數.xlsx
+++ b/ML2025Spring/最終分數.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t xml:space="preserve">Private Score</t>
   </si>
@@ -163,21 +163,6 @@
   </si>
   <si>
     <t xml:space="preserve">HW10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW15</t>
   </si>
 </sst>
 </file>
@@ -443,7 +428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="12.11328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.01"/>
@@ -617,13 +602,15 @@
       <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -653,9 +640,7 @@
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -666,9 +651,7 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -679,9 +662,7 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -692,9 +673,7 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -705,9 +684,7 @@
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -11486,61 +11463,11 @@
       <c r="H995" s="2"/>
       <c r="I995" s="4"/>
     </row>
-    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-      <c r="H996" s="2"/>
-      <c r="I996" s="4"/>
-    </row>
-    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
-      <c r="E997" s="2"/>
-      <c r="F997" s="2"/>
-      <c r="G997" s="2"/>
-      <c r="H997" s="2"/>
-      <c r="I997" s="4"/>
-    </row>
-    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
-      <c r="E998" s="2"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-      <c r="H998" s="2"/>
-      <c r="I998" s="4"/>
-    </row>
-    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
-      <c r="E999" s="2"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-      <c r="H999" s="2"/>
-      <c r="I999" s="4"/>
-    </row>
-    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
-      <c r="E1000" s="2"/>
-      <c r="F1000" s="2"/>
-      <c r="G1000" s="2"/>
-      <c r="H1000" s="2"/>
-      <c r="I1000" s="4"/>
-    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/ML2025Spring/最終分數.xlsx
+++ b/ML2025Spring/最終分數.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t xml:space="preserve">Private Score</t>
   </si>
@@ -162,6 +162,23 @@
     <t xml:space="preserve">HW09</t>
   </si>
   <si>
+    <t xml:space="preserve">手動對前十題答案 
+GSM8K: 7/10, ARC: 7/10
+理論上有機會超過 Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong
+ARC Acc. ≥ 56%
+GSM8K Acc. ≥ 48% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">重點在選擇 MERGE_TYPE = "dare_ties"
+ 但 density = 0.7 不能太高或太低
+這個 weight_math = 1.0 要很高，因為數學邏輯很容易錯
+ 這個 weight_science = 0.2 要低一點，因為題目對 AI 來說較簡單，
+所以低一點 merge 時才不會干擾 math 的部分</t>
+  </si>
+  <si>
     <t xml:space="preserve">HW10</t>
   </si>
 </sst>
@@ -268,7 +285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -303,6 +320,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -436,7 +457,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="57.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="62.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="36.73"/>
   </cols>
   <sheetData>
@@ -613,22 +634,28 @@
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="E10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>

--- a/ML2025Spring/最終分數.xlsx
+++ b/ML2025Spring/最終分數.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t xml:space="preserve">Private Score</t>
   </si>
@@ -180,6 +180,23 @@
   </si>
   <si>
     <t xml:space="preserve">HW10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DINO Score CLIP-T 
+Object-1 68 18 
+Object-2 60 17 
+Object-3 61 18 
+Object-4 68 19 
+Object-5 60 19 
+Object-6 57 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重點在個別調參，
+但 Object-2 眼鏡一直都是粉紅色，
+Object-5 霍爾的移動城堡下雪有時不會對，
+Object-6 的烏龜最難，要麻沒盤子要麻長得不是烏龜，即使 seed 都一樣了，同樣的參數不見得能出一樣的好結果
+因為不知道分數 model 如何判讀，最後只能以肉眼找出較好的參數，
+程式最後也有用不同的參數去產生圖片，依個人喜好進行選擇</t>
   </si>
 </sst>
 </file>
@@ -653,7 +670,7 @@
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
@@ -661,9 +678,13 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
